--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104526_W8.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104526_W8.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>A. PUSTOVYI</t>
+          <t>Y. PONS</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,64 +565,64 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>2.5518</v>
+        <v>2.3628</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.2573</v>
+        <v>1.1284</v>
       </c>
       <c r="F2" t="n">
-        <v>2.8091</v>
+        <v>1.2345</v>
       </c>
       <c r="G2" t="n">
-        <v>2.7082</v>
+        <v>2.1036</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.3145</v>
+        <v>0.2404</v>
       </c>
       <c r="I2" t="n">
-        <v>3.0228</v>
+        <v>1.8632</v>
       </c>
       <c r="J2" t="n">
-        <v>1.8326</v>
+        <v>2.1738</v>
       </c>
       <c r="K2" t="n">
-        <v>-0.1079</v>
+        <v>0.9308</v>
       </c>
       <c r="L2" t="n">
-        <v>1.9405</v>
+        <v>1.243</v>
       </c>
       <c r="M2" t="n">
-        <v>0.8757</v>
+        <v>-0.0703</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.2066</v>
+        <v>-0.6904</v>
       </c>
       <c r="O2" t="n">
-        <v>1.0823</v>
+        <v>0.6201</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="Q2" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R2" t="n">
-        <v>0.9073</v>
+        <v>1.3658</v>
       </c>
       <c r="S2" t="n">
-        <v>0.0704</v>
+        <v>-1.0579</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.9557</v>
+        <v>-0.9968</v>
       </c>
       <c r="U2" t="n">
-        <v>1.0262</v>
+        <v>-0.0611</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>1.0895</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>1.0895</v>
       </c>
       <c r="X2" t="n">
         <v>0</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Y. PONS</t>
+          <t>A. PUSTOVYI</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,64 +643,64 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.3312</v>
+        <v>2.1885</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9717</v>
+        <v>0.068</v>
       </c>
       <c r="F3" t="n">
-        <v>1.3595</v>
+        <v>2.1205</v>
       </c>
       <c r="G3" t="n">
-        <v>2.096</v>
+        <v>2.7144</v>
       </c>
       <c r="H3" t="n">
-        <v>0.2249</v>
+        <v>-0.3159</v>
       </c>
       <c r="I3" t="n">
-        <v>1.8711</v>
+        <v>3.0302</v>
       </c>
       <c r="J3" t="n">
-        <v>2.1958</v>
+        <v>1.8082</v>
       </c>
       <c r="K3" t="n">
-        <v>0.9351</v>
+        <v>-0.1281</v>
       </c>
       <c r="L3" t="n">
-        <v>1.2607</v>
+        <v>1.9363</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.0998</v>
+        <v>0.9062</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.7103</v>
+        <v>-0.1877</v>
       </c>
       <c r="O3" t="n">
-        <v>0.6105</v>
+        <v>1.0939</v>
       </c>
       <c r="P3" t="n">
-        <v>0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R3" t="n">
-        <v>1.361</v>
+        <v>0.9105</v>
       </c>
       <c r="S3" t="n">
-        <v>-1.0843</v>
+        <v>-0.2982</v>
       </c>
       <c r="T3" t="n">
-        <v>-1.1825</v>
+        <v>-0.602</v>
       </c>
       <c r="U3" t="n">
-        <v>0.0983</v>
+        <v>0.3038</v>
       </c>
       <c r="V3" t="n">
-        <v>1.0927</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>1.0927</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
@@ -721,67 +721,67 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.5762</v>
+        <v>1.4746</v>
       </c>
       <c r="E4" t="n">
-        <v>1.7963</v>
+        <v>1.5794</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.2201</v>
+        <v>-0.1048</v>
       </c>
       <c r="G4" t="n">
-        <v>1.3084</v>
+        <v>1.3245</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.3523</v>
+        <v>-0.3396</v>
       </c>
       <c r="I4" t="n">
-        <v>1.6607</v>
+        <v>1.6641</v>
       </c>
       <c r="J4" t="n">
-        <v>1.4273</v>
+        <v>1.4239</v>
       </c>
       <c r="K4" t="n">
-        <v>0.1212</v>
+        <v>0.1207</v>
       </c>
       <c r="L4" t="n">
-        <v>1.3061</v>
+        <v>1.3033</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.1189</v>
+        <v>-0.09950000000000001</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.4735</v>
+        <v>-0.4603</v>
       </c>
       <c r="O4" t="n">
-        <v>0.3546</v>
+        <v>0.3608</v>
       </c>
       <c r="P4" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.2519</v>
+        <v>-0.375</v>
       </c>
       <c r="T4" t="n">
-        <v>0.369</v>
+        <v>0.1555</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.6209</v>
+        <v>-0.5304</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.1607</v>
+        <v>-0.1578</v>
       </c>
       <c r="W4" t="n">
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.1607</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="5">
@@ -799,19 +799,19 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.7093</v>
+        <v>0.2694</v>
       </c>
       <c r="E5" t="n">
-        <v>0.8080000000000001</v>
+        <v>0.3342</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.09859999999999999</v>
+        <v>-0.0648</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.3463</v>
+        <v>-0.3447</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.3463</v>
+        <v>-0.3447</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -826,37 +826,37 @@
         <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.3463</v>
+        <v>-0.3447</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.3463</v>
+        <v>-0.3447</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="S5" t="n">
-        <v>0.6681</v>
+        <v>0.2287</v>
       </c>
       <c r="T5" t="n">
-        <v>0.6472</v>
+        <v>0.1765</v>
       </c>
       <c r="U5" t="n">
-        <v>0.0209</v>
+        <v>0.0523</v>
       </c>
       <c r="V5" t="n">
-        <v>0.1607</v>
+        <v>0.1578</v>
       </c>
       <c r="W5" t="n">
-        <v>0.1607</v>
+        <v>0.1578</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
@@ -877,58 +877,58 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.3122</v>
+        <v>-0.1245</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.8374</v>
+        <v>-1.1288</v>
       </c>
       <c r="F6" t="n">
-        <v>1.1496</v>
+        <v>1.0043</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.8568</v>
+        <v>-0.855</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.5209</v>
+        <v>-0.5199</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.3359</v>
+        <v>-0.3351</v>
       </c>
       <c r="J6" t="n">
-        <v>-1.2064</v>
+        <v>-1.2145</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.4573</v>
+        <v>-0.4621</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.749</v>
+        <v>-0.7524</v>
       </c>
       <c r="M6" t="n">
-        <v>0.3496</v>
+        <v>0.3595</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.0636</v>
+        <v>-0.0578</v>
       </c>
       <c r="O6" t="n">
-        <v>0.4132</v>
+        <v>0.4173</v>
       </c>
       <c r="P6" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="S6" t="n">
-        <v>0.4884</v>
+        <v>0.0476</v>
       </c>
       <c r="T6" t="n">
-        <v>0.369</v>
+        <v>0.0858</v>
       </c>
       <c r="U6" t="n">
-        <v>0.1195</v>
+        <v>-0.0381</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A. BEST</t>
+          <t>R. GUERRERO</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.2728</v>
+        <v>-0.4375</v>
       </c>
       <c r="E7" t="n">
-        <v>0.703</v>
+        <v>0.1684</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.9759</v>
+        <v>-0.6059</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.9596</v>
+        <v>-1.1645</v>
       </c>
       <c r="H7" t="n">
-        <v>-3.3186</v>
+        <v>-0.7729</v>
       </c>
       <c r="I7" t="n">
-        <v>2.359</v>
+        <v>-0.3916</v>
       </c>
       <c r="J7" t="n">
-        <v>0.2947</v>
+        <v>0.1407</v>
       </c>
       <c r="K7" t="n">
-        <v>-2.2001</v>
+        <v>0.1034</v>
       </c>
       <c r="L7" t="n">
-        <v>2.4948</v>
+        <v>0.0372</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.2543</v>
+        <v>-1.3052</v>
       </c>
       <c r="N7" t="n">
-        <v>-1.1185</v>
+        <v>-0.8763</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.1359</v>
+        <v>-0.4289</v>
       </c>
       <c r="P7" t="n">
-        <v>2.0415</v>
+        <v>0.9105</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>2.0415</v>
+        <v>0.9105</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.1013</v>
+        <v>-0.1835</v>
       </c>
       <c r="T7" t="n">
-        <v>0.4083</v>
+        <v>0.0278</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.5096000000000001</v>
+        <v>-0.2113</v>
       </c>
       <c r="V7" t="n">
-        <v>-1.2534</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.2534</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -1033,58 +1033,58 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.3808</v>
+        <v>-0.5600000000000001</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.383</v>
+        <v>-0.482</v>
       </c>
       <c r="F8" t="n">
-        <v>0.0022</v>
+        <v>-0.078</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.9242</v>
+        <v>-1.9176</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.2742</v>
+        <v>-0.2702</v>
       </c>
       <c r="I8" t="n">
-        <v>-1.6499</v>
+        <v>-1.6474</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.6825</v>
+        <v>-0.6862</v>
       </c>
       <c r="K8" t="n">
-        <v>0.1039</v>
+        <v>0.1034</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.7864</v>
+        <v>-0.7896</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.2417</v>
+        <v>-1.2314</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.3781</v>
+        <v>-0.3736</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.8636</v>
+        <v>-0.8578</v>
       </c>
       <c r="P8" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="S8" t="n">
-        <v>0.1824</v>
+        <v>-0.008200000000000001</v>
       </c>
       <c r="T8" t="n">
-        <v>0.2994</v>
+        <v>0.2042</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.1171</v>
+        <v>-0.2124</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>R. GUERRERO</t>
+          <t>A. BEST</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.8856000000000001</v>
+        <v>-0.6892</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.2066</v>
+        <v>0.09660000000000001</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.679</v>
+        <v>-0.7858000000000001</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.1723</v>
+        <v>-0.976</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.7778</v>
+        <v>-3.3309</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.3945</v>
+        <v>2.3549</v>
       </c>
       <c r="J9" t="n">
-        <v>0.1412</v>
+        <v>0.255</v>
       </c>
       <c r="K9" t="n">
-        <v>0.1039</v>
+        <v>-2.2245</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0373</v>
+        <v>2.4795</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.3135</v>
+        <v>-1.231</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.8817</v>
+        <v>-1.1064</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.4318</v>
+        <v>-0.1246</v>
       </c>
       <c r="P9" t="n">
-        <v>0.9073</v>
+        <v>2.0487</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>0.9073</v>
+        <v>2.0487</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.6206</v>
+        <v>-0.5145999999999999</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.3478</v>
+        <v>-0.1584</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.2728</v>
+        <v>-0.3562</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>-1.2472</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>-1.2472</v>
       </c>
     </row>
     <row r="10">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.6947</v>
+        <v>-1.314</v>
       </c>
       <c r="E10" t="n">
-        <v>0.3965</v>
+        <v>0.6985</v>
       </c>
       <c r="F10" t="n">
-        <v>-2.0912</v>
+        <v>-2.0125</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.1801</v>
+        <v>-0.1779</v>
       </c>
       <c r="H10" t="n">
-        <v>0.6248</v>
+        <v>0.6233</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.805</v>
+        <v>-0.8012</v>
       </c>
       <c r="J10" t="n">
-        <v>0.8139</v>
+        <v>0.8101</v>
       </c>
       <c r="K10" t="n">
-        <v>0.8139</v>
+        <v>0.8101</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.994</v>
+        <v>-0.9881</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.1891</v>
+        <v>-0.1868</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.805</v>
+        <v>-0.8012</v>
       </c>
       <c r="P10" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.4633</v>
+        <v>-0.0953</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.4174</v>
+        <v>-0.1116</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.046</v>
+        <v>0.0163</v>
       </c>
       <c r="V10" t="n">
-        <v>-2.1853</v>
+        <v>-2.1789</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-2.1853</v>
+        <v>-2.1789</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>K. KURIC</t>
+          <t>S. EVANS</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1267,73 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.8091</v>
+        <v>-2.2736</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.3751</v>
+        <v>1.9139</v>
       </c>
       <c r="F11" t="n">
-        <v>0.5659999999999999</v>
+        <v>-4.1875</v>
       </c>
       <c r="G11" t="n">
-        <v>-1.9654</v>
+        <v>0.9197</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.5207000000000001</v>
+        <v>1.3473</v>
       </c>
       <c r="I11" t="n">
-        <v>-1.4448</v>
+        <v>-0.4276</v>
       </c>
       <c r="J11" t="n">
-        <v>-2.1693</v>
+        <v>2.6663</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.3299</v>
+        <v>2.5403</v>
       </c>
       <c r="L11" t="n">
-        <v>-1.8393</v>
+        <v>0.1259</v>
       </c>
       <c r="M11" t="n">
-        <v>0.2038</v>
+        <v>-1.7466</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.1908</v>
+        <v>-1.1931</v>
       </c>
       <c r="O11" t="n">
-        <v>0.3946</v>
+        <v>-0.5535</v>
       </c>
       <c r="P11" t="n">
-        <v>-1.361</v>
+        <v>-1.1382</v>
       </c>
       <c r="Q11" t="n">
-        <v>-2.2683</v>
+        <v>-3.4145</v>
       </c>
       <c r="R11" t="n">
-        <v>0.9073</v>
+        <v>2.2763</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.4146</v>
+        <v>-0.8942</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.0302</v>
+        <v>-0.6926</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.3844</v>
+        <v>-0.2016</v>
       </c>
       <c r="V11" t="n">
-        <v>0.9320000000000001</v>
+        <v>-1.1609</v>
       </c>
       <c r="W11" t="n">
-        <v>1.0927</v>
+        <v>3.3547</v>
       </c>
       <c r="X11" t="n">
-        <v>-0.1607</v>
+        <v>-4.5157</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>S. EVANS</t>
+          <t>K. KURIC</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-3.0548</v>
+        <v>-2.3026</v>
       </c>
       <c r="E12" t="n">
-        <v>1.3757</v>
+        <v>-3.2452</v>
       </c>
       <c r="F12" t="n">
-        <v>-4.4305</v>
+        <v>0.9426</v>
       </c>
       <c r="G12" t="n">
-        <v>0.9256</v>
+        <v>-1.9858</v>
       </c>
       <c r="H12" t="n">
-        <v>1.3521</v>
+        <v>-0.5362</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.4265</v>
+        <v>-1.4496</v>
       </c>
       <c r="J12" t="n">
-        <v>2.7071</v>
+        <v>-2.2182</v>
       </c>
       <c r="K12" t="n">
-        <v>2.566</v>
+        <v>-0.3629</v>
       </c>
       <c r="L12" t="n">
-        <v>0.1411</v>
+        <v>-1.8553</v>
       </c>
       <c r="M12" t="n">
-        <v>-1.7815</v>
+        <v>0.2324</v>
       </c>
       <c r="N12" t="n">
-        <v>-1.2139</v>
+        <v>-0.1733</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.5676</v>
+        <v>0.4057</v>
       </c>
       <c r="P12" t="n">
-        <v>-1.1342</v>
+        <v>-1.3658</v>
       </c>
       <c r="Q12" t="n">
-        <v>-3.4025</v>
+        <v>-2.2763</v>
       </c>
       <c r="R12" t="n">
-        <v>2.2683</v>
+        <v>0.9105</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.6895</v>
+        <v>0.1173</v>
       </c>
       <c r="T12" t="n">
-        <v>-1.3035</v>
+        <v>0.1599</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.3859</v>
+        <v>-0.0425</v>
       </c>
       <c r="V12" t="n">
-        <v>-1.1568</v>
+        <v>0.9317</v>
       </c>
       <c r="W12" t="n">
-        <v>3.3746</v>
+        <v>1.0895</v>
       </c>
       <c r="X12" t="n">
-        <v>-4.5314</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="13">
@@ -1423,67 +1423,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-4.9785</v>
+        <v>-4.1372</v>
       </c>
       <c r="E13" t="n">
-        <v>-5.6308</v>
+        <v>-5.009</v>
       </c>
       <c r="F13" t="n">
-        <v>0.6522</v>
+        <v>0.8718</v>
       </c>
       <c r="G13" t="n">
-        <v>-3.8037</v>
+        <v>-3.8052</v>
       </c>
       <c r="H13" t="n">
-        <v>0.0534</v>
+        <v>0.0545</v>
       </c>
       <c r="I13" t="n">
-        <v>-3.857</v>
+        <v>-3.8597</v>
       </c>
       <c r="J13" t="n">
-        <v>-2.3652</v>
+        <v>-2.3886</v>
       </c>
       <c r="K13" t="n">
-        <v>0.6682</v>
+        <v>0.6583</v>
       </c>
       <c r="L13" t="n">
-        <v>-3.0335</v>
+        <v>-3.0469</v>
       </c>
       <c r="M13" t="n">
-        <v>-1.4384</v>
+        <v>-1.4166</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.6149</v>
+        <v>-0.6037</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.8236</v>
+        <v>-0.8129</v>
       </c>
       <c r="P13" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="Q13" t="n">
-        <v>-3.4025</v>
+        <v>-3.4145</v>
       </c>
       <c r="R13" t="n">
-        <v>2.2683</v>
+        <v>2.2763</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.9727</v>
+        <v>-0.1255</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.9557</v>
+        <v>-0.2954</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.0169</v>
+        <v>0.1699</v>
       </c>
       <c r="V13" t="n">
-        <v>0.9320000000000001</v>
+        <v>0.9317</v>
       </c>
       <c r="W13" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X13" t="n">
-        <v>-0.1607</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="14">
@@ -1501,67 +1501,67 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-6.595600000000001</v>
+        <v>-5.543300000000001</v>
       </c>
       <c r="E14" t="n">
-        <v>-4.639</v>
+        <v>-3.877600000000001</v>
       </c>
       <c r="F14" t="n">
-        <v>-1.956700000000001</v>
+        <v>-1.6656</v>
       </c>
       <c r="G14" t="n">
-        <v>-4.1702</v>
+        <v>-4.1645</v>
       </c>
       <c r="H14" t="n">
-        <v>-4.1701</v>
+        <v>-4.164800000000001</v>
       </c>
       <c r="I14" t="n">
-        <v>8.881784197001252e-16</v>
+        <v>0.0001999999999995339</v>
       </c>
       <c r="J14" t="n">
-        <v>2.989200000000002</v>
+        <v>2.770500000000001</v>
       </c>
       <c r="K14" t="n">
-        <v>2.217</v>
+        <v>2.0894</v>
       </c>
       <c r="L14" t="n">
-        <v>0.7722999999999995</v>
+        <v>0.6809999999999992</v>
       </c>
       <c r="M14" t="n">
-        <v>-7.1593</v>
+        <v>-6.9353</v>
       </c>
       <c r="N14" t="n">
-        <v>-6.3873</v>
+        <v>-6.2541</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.7723</v>
+        <v>-0.6811000000000003</v>
       </c>
       <c r="P14" t="n">
-        <v>3.4024</v>
+        <v>3.4144</v>
       </c>
       <c r="Q14" t="n">
-        <v>-11.3417</v>
+        <v>-11.3817</v>
       </c>
       <c r="R14" t="n">
-        <v>14.744</v>
+        <v>14.796</v>
       </c>
       <c r="S14" t="n">
-        <v>-4.1889</v>
+        <v>-3.1588</v>
       </c>
       <c r="T14" t="n">
-        <v>-3.099900000000001</v>
+        <v>-2.0471</v>
       </c>
       <c r="U14" t="n">
-        <v>-1.0887</v>
+        <v>-1.1113</v>
       </c>
       <c r="V14" t="n">
-        <v>-1.6388</v>
+        <v>-1.6341</v>
       </c>
       <c r="W14" t="n">
-        <v>6.8134</v>
+        <v>6.781</v>
       </c>
       <c r="X14" t="n">
-        <v>-8.452199999999999</v>
+        <v>-8.415199999999999</v>
       </c>
     </row>
     <row r="15">
@@ -1579,64 +1579,64 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>4.8929</v>
+        <v>3.7128</v>
       </c>
       <c r="E15" t="n">
-        <v>2.2927</v>
+        <v>1.3036</v>
       </c>
       <c r="F15" t="n">
-        <v>2.6002</v>
+        <v>2.4092</v>
       </c>
       <c r="G15" t="n">
-        <v>1.7009</v>
+        <v>1.6933</v>
       </c>
       <c r="H15" t="n">
-        <v>0.4187</v>
+        <v>0.403</v>
       </c>
       <c r="I15" t="n">
-        <v>1.2822</v>
+        <v>1.2904</v>
       </c>
       <c r="J15" t="n">
-        <v>1.0762</v>
+        <v>1.0453</v>
       </c>
       <c r="K15" t="n">
-        <v>0.4045</v>
+        <v>0.375</v>
       </c>
       <c r="L15" t="n">
-        <v>0.6717</v>
+        <v>0.6703</v>
       </c>
       <c r="M15" t="n">
-        <v>0.6247</v>
+        <v>0.6481</v>
       </c>
       <c r="N15" t="n">
-        <v>0.0142</v>
+        <v>0.028</v>
       </c>
       <c r="O15" t="n">
-        <v>0.6105</v>
+        <v>0.6201</v>
       </c>
       <c r="P15" t="n">
-        <v>-1.361</v>
+        <v>-1.3658</v>
       </c>
       <c r="Q15" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="R15" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="S15" t="n">
-        <v>2.5925</v>
+        <v>1.4355</v>
       </c>
       <c r="T15" t="n">
-        <v>1.5243</v>
+        <v>0.5849</v>
       </c>
       <c r="U15" t="n">
-        <v>1.0682</v>
+        <v>0.8506</v>
       </c>
       <c r="V15" t="n">
-        <v>1.9604</v>
+        <v>1.9497</v>
       </c>
       <c r="W15" t="n">
-        <v>1.9604</v>
+        <v>1.9497</v>
       </c>
       <c r="X15" t="n">
         <v>0</v>
@@ -1657,67 +1657,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.5161</v>
+        <v>2.8772</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.7073</v>
+        <v>-0.4152</v>
       </c>
       <c r="F16" t="n">
-        <v>3.2234</v>
+        <v>3.2924</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.1915</v>
+        <v>-0.2059</v>
       </c>
       <c r="H16" t="n">
-        <v>0.9467</v>
+        <v>0.9368</v>
       </c>
       <c r="I16" t="n">
-        <v>-1.1382</v>
+        <v>-1.1427</v>
       </c>
       <c r="J16" t="n">
-        <v>-1.488</v>
+        <v>-1.5278</v>
       </c>
       <c r="K16" t="n">
-        <v>0.9484</v>
+        <v>0.9233</v>
       </c>
       <c r="L16" t="n">
-        <v>-2.4364</v>
+        <v>-2.4511</v>
       </c>
       <c r="M16" t="n">
-        <v>1.2965</v>
+        <v>1.3219</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.0017</v>
+        <v>0.0135</v>
       </c>
       <c r="O16" t="n">
-        <v>1.2982</v>
+        <v>1.3083</v>
       </c>
       <c r="P16" t="n">
-        <v>-2.0415</v>
+        <v>-2.0487</v>
       </c>
       <c r="Q16" t="n">
-        <v>-3.4025</v>
+        <v>-3.4145</v>
       </c>
       <c r="R16" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="S16" t="n">
-        <v>0.6998</v>
+        <v>1.0894</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.1875</v>
+        <v>0.1691</v>
       </c>
       <c r="U16" t="n">
-        <v>0.8873</v>
+        <v>0.9203</v>
       </c>
       <c r="V16" t="n">
-        <v>4.0492</v>
+        <v>4.0424</v>
       </c>
       <c r="W16" t="n">
-        <v>4.3707</v>
+        <v>4.3579</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.3214</v>
+        <v>-0.3155</v>
       </c>
     </row>
     <row r="17">
@@ -1735,58 +1735,58 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>2.2287</v>
+        <v>2.5411</v>
       </c>
       <c r="E17" t="n">
-        <v>2.6203</v>
+        <v>2.8388</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.3916</v>
+        <v>-0.2977</v>
       </c>
       <c r="G17" t="n">
-        <v>1.6985</v>
+        <v>1.7084</v>
       </c>
       <c r="H17" t="n">
-        <v>0.5337</v>
+        <v>0.5451</v>
       </c>
       <c r="I17" t="n">
-        <v>1.1648</v>
+        <v>1.1633</v>
       </c>
       <c r="J17" t="n">
-        <v>3.8724</v>
+        <v>3.8565</v>
       </c>
       <c r="K17" t="n">
-        <v>1.039</v>
+        <v>1.0342</v>
       </c>
       <c r="L17" t="n">
-        <v>2.8334</v>
+        <v>2.8223</v>
       </c>
       <c r="M17" t="n">
-        <v>-2.1738</v>
+        <v>-2.1481</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.5053</v>
+        <v>-0.4891</v>
       </c>
       <c r="O17" t="n">
-        <v>-1.6685</v>
+        <v>-1.659</v>
       </c>
       <c r="P17" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="Q17" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R17" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="S17" t="n">
-        <v>0.3033</v>
+        <v>0.605</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.1179</v>
+        <v>0.1204</v>
       </c>
       <c r="U17" t="n">
-        <v>0.4213</v>
+        <v>0.4846</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Y. KRAAG</t>
+          <t>C. HUNT</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,64 +1813,64 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>1.7328</v>
+        <v>1.2729</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.2021</v>
+        <v>0.5834</v>
       </c>
       <c r="F18" t="n">
-        <v>2.9349</v>
+        <v>0.6896</v>
       </c>
       <c r="G18" t="n">
-        <v>-1.3857</v>
+        <v>0.0005999999999999999</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.0636</v>
+        <v>0.7813</v>
       </c>
       <c r="I18" t="n">
-        <v>-1.3221</v>
+        <v>-0.7806999999999999</v>
       </c>
       <c r="J18" t="n">
-        <v>-2.3408</v>
+        <v>1.388</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.09370000000000001</v>
+        <v>1.2993</v>
       </c>
       <c r="L18" t="n">
-        <v>-2.2471</v>
+        <v>0.0887</v>
       </c>
       <c r="M18" t="n">
-        <v>0.9550999999999999</v>
+        <v>-1.3874</v>
       </c>
       <c r="N18" t="n">
-        <v>0.0301</v>
+        <v>-0.518</v>
       </c>
       <c r="O18" t="n">
-        <v>0.925</v>
+        <v>-0.8694</v>
       </c>
       <c r="P18" t="n">
-        <v>1.1342</v>
+        <v>0.6829</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>-1.1382</v>
       </c>
       <c r="R18" t="n">
-        <v>1.1342</v>
+        <v>1.8211</v>
       </c>
       <c r="S18" t="n">
-        <v>2.3699</v>
+        <v>0.2739</v>
       </c>
       <c r="T18" t="n">
-        <v>1.5243</v>
+        <v>0.018</v>
       </c>
       <c r="U18" t="n">
-        <v>0.8456</v>
+        <v>0.2559</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.3856</v>
+        <v>0.3155</v>
       </c>
       <c r="W18" t="n">
-        <v>-0.3856</v>
+        <v>0.3155</v>
       </c>
       <c r="X18" t="n">
         <v>0</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>C. HUNT</t>
+          <t>Y. KRAAG</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,64 +1891,64 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.9809</v>
+        <v>0.6149</v>
       </c>
       <c r="E19" t="n">
-        <v>0.8613</v>
+        <v>-2.1594</v>
       </c>
       <c r="F19" t="n">
-        <v>0.1195</v>
+        <v>2.7743</v>
       </c>
       <c r="G19" t="n">
-        <v>0.0037</v>
+        <v>-1.379</v>
       </c>
       <c r="H19" t="n">
-        <v>0.7821</v>
+        <v>-0.0578</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.7784</v>
+        <v>-1.3213</v>
       </c>
       <c r="J19" t="n">
-        <v>1.423</v>
+        <v>-2.3574</v>
       </c>
       <c r="K19" t="n">
-        <v>1.3192</v>
+        <v>-0.1002</v>
       </c>
       <c r="L19" t="n">
-        <v>0.1038</v>
+        <v>-2.2572</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.4193</v>
+        <v>0.9784</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.5371</v>
+        <v>0.0424</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.8822</v>
+        <v>0.9360000000000001</v>
       </c>
       <c r="P19" t="n">
-        <v>0.6805</v>
+        <v>1.1382</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.1342</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>1.8147</v>
+        <v>1.1382</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.0248</v>
+        <v>1.2427</v>
       </c>
       <c r="T19" t="n">
-        <v>0.2511</v>
+        <v>0.5849</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.2758</v>
+        <v>0.6578000000000001</v>
       </c>
       <c r="V19" t="n">
-        <v>0.3214</v>
+        <v>-0.387</v>
       </c>
       <c r="W19" t="n">
-        <v>0.3214</v>
+        <v>-0.387</v>
       </c>
       <c r="X19" t="n">
         <v>0</v>
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.0794</v>
+        <v>0.5368000000000001</v>
       </c>
       <c r="E20" t="n">
-        <v>0.5451</v>
+        <v>0.979</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.6245000000000001</v>
+        <v>-0.4422</v>
       </c>
       <c r="G20" t="n">
-        <v>0.7074</v>
+        <v>0.6921</v>
       </c>
       <c r="H20" t="n">
-        <v>0.5209</v>
+        <v>0.5199</v>
       </c>
       <c r="I20" t="n">
-        <v>0.1865</v>
+        <v>0.1722</v>
       </c>
       <c r="J20" t="n">
-        <v>2.4445</v>
+        <v>2.4101</v>
       </c>
       <c r="K20" t="n">
-        <v>0.9626</v>
+        <v>0.9513</v>
       </c>
       <c r="L20" t="n">
-        <v>1.4818</v>
+        <v>1.4588</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.7371</v>
+        <v>-1.718</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.4417</v>
+        <v>-0.4314</v>
       </c>
       <c r="O20" t="n">
-        <v>-1.2954</v>
+        <v>-1.2866</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R20" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.7848000000000001</v>
+        <v>-0.1568</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.7652</v>
+        <v>-0.2929</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.0197</v>
+        <v>0.1361</v>
       </c>
       <c r="V20" t="n">
-        <v>0.2249</v>
+        <v>0.2292</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>0.2249</v>
+        <v>0.2292</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>S. BIRGANDER</t>
+          <t>M. RUZIC</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.389</v>
+        <v>-0.0708</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.6148</v>
+        <v>-0.6317</v>
       </c>
       <c r="F21" t="n">
-        <v>0.2258</v>
+        <v>0.5609</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.307</v>
+        <v>1.6145</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.2884</v>
+        <v>-0.5888</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.0186</v>
+        <v>2.2033</v>
       </c>
       <c r="J21" t="n">
-        <v>0.9155</v>
+        <v>0.4509</v>
       </c>
       <c r="K21" t="n">
-        <v>0.1692</v>
+        <v>-0.7035</v>
       </c>
       <c r="L21" t="n">
-        <v>0.7463</v>
+        <v>1.1543</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.2225</v>
+        <v>1.1636</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.4576</v>
+        <v>0.1146</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.7649</v>
+        <v>1.049</v>
       </c>
       <c r="P21" t="n">
-        <v>-0.9073</v>
+        <v>-0.6829</v>
       </c>
       <c r="Q21" t="n">
-        <v>-2.2683</v>
+        <v>-1.1382</v>
       </c>
       <c r="R21" t="n">
-        <v>1.361</v>
+        <v>0.4553</v>
       </c>
       <c r="S21" t="n">
-        <v>0.8254</v>
+        <v>0.0871</v>
       </c>
       <c r="T21" t="n">
-        <v>0.738</v>
+        <v>0.0556</v>
       </c>
       <c r="U21" t="n">
-        <v>0.08740000000000001</v>
+        <v>0.0316</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>-1.0895</v>
       </c>
       <c r="W21" t="n">
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>M. RUZIC</t>
+          <t>A. HANGA</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.7682</v>
+        <v>-0.8458</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.0945</v>
+        <v>0.5888</v>
       </c>
       <c r="F22" t="n">
-        <v>0.3262</v>
+        <v>-1.4346</v>
       </c>
       <c r="G22" t="n">
-        <v>1.6089</v>
+        <v>-0.8666</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.5901999999999999</v>
+        <v>1.0967</v>
       </c>
       <c r="I22" t="n">
-        <v>2.1991</v>
+        <v>-1.9633</v>
       </c>
       <c r="J22" t="n">
-        <v>0.457</v>
+        <v>0.9236</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.6998</v>
+        <v>1.7582</v>
       </c>
       <c r="L22" t="n">
-        <v>1.1568</v>
+        <v>-0.8345</v>
       </c>
       <c r="M22" t="n">
-        <v>1.1519</v>
+        <v>-1.7902</v>
       </c>
       <c r="N22" t="n">
-        <v>0.1096</v>
+        <v>-0.6615</v>
       </c>
       <c r="O22" t="n">
-        <v>1.0423</v>
+        <v>-1.1287</v>
       </c>
       <c r="P22" t="n">
-        <v>-0.6805</v>
+        <v>0.4553</v>
       </c>
       <c r="Q22" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R22" t="n">
-        <v>0.4537</v>
+        <v>1.5934</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.604</v>
+        <v>0.1103</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.4174</v>
+        <v>-0.2861</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.1866</v>
+        <v>0.3964</v>
       </c>
       <c r="V22" t="n">
-        <v>-1.0927</v>
+        <v>-0.5447</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>1.0895</v>
       </c>
       <c r="X22" t="n">
-        <v>-1.0927</v>
+        <v>-1.6342</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A. HANGA</t>
+          <t>S. BIRGANDER</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-1.6235</v>
+        <v>-0.9520999999999999</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.2145</v>
+        <v>-1.2333</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.409</v>
+        <v>0.2812</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.8766</v>
+        <v>-0.3098</v>
       </c>
       <c r="H23" t="n">
-        <v>1.0878</v>
+        <v>-0.2982</v>
       </c>
       <c r="I23" t="n">
-        <v>-1.9645</v>
+        <v>-0.0116</v>
       </c>
       <c r="J23" t="n">
-        <v>0.9399</v>
+        <v>0.8924</v>
       </c>
       <c r="K23" t="n">
-        <v>1.7663</v>
+        <v>0.1477</v>
       </c>
       <c r="L23" t="n">
-        <v>-0.8264</v>
+        <v>0.7447</v>
       </c>
       <c r="M23" t="n">
-        <v>-1.8166</v>
+        <v>-1.2022</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.6785</v>
+        <v>-0.4458</v>
       </c>
       <c r="O23" t="n">
-        <v>-1.1381</v>
+        <v>-0.7563</v>
       </c>
       <c r="P23" t="n">
-        <v>0.4537</v>
+        <v>-0.9105</v>
       </c>
       <c r="Q23" t="n">
-        <v>-1.1342</v>
+        <v>-2.2763</v>
       </c>
       <c r="R23" t="n">
-        <v>1.5878</v>
+        <v>1.3658</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.6542</v>
+        <v>0.2682</v>
       </c>
       <c r="T23" t="n">
-        <v>-1.113</v>
+        <v>0.1506</v>
       </c>
       <c r="U23" t="n">
-        <v>0.4588</v>
+        <v>0.1176</v>
       </c>
       <c r="V23" t="n">
-        <v>-0.5463</v>
+        <v>0</v>
       </c>
       <c r="W23" t="n">
-        <v>1.0927</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>-1.639</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-2.8957</v>
+        <v>-2.3087</v>
       </c>
       <c r="E24" t="n">
-        <v>-1.6222</v>
+        <v>-1.2777</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.2735</v>
+        <v>-1.031</v>
       </c>
       <c r="G24" t="n">
-        <v>1.2116</v>
+        <v>1.2172</v>
       </c>
       <c r="H24" t="n">
-        <v>0.8224</v>
+        <v>0.8269</v>
       </c>
       <c r="I24" t="n">
-        <v>0.3892</v>
+        <v>0.3903</v>
       </c>
       <c r="J24" t="n">
-        <v>-0.1403</v>
+        <v>-0.1464</v>
       </c>
       <c r="K24" t="n">
-        <v>0.5715</v>
+        <v>0.5688</v>
       </c>
       <c r="L24" t="n">
-        <v>-0.7117</v>
+        <v>-0.7151999999999999</v>
       </c>
       <c r="M24" t="n">
-        <v>1.3519</v>
+        <v>1.3636</v>
       </c>
       <c r="N24" t="n">
-        <v>0.251</v>
+        <v>0.2581</v>
       </c>
       <c r="O24" t="n">
-        <v>1.1009</v>
+        <v>1.1055</v>
       </c>
       <c r="P24" t="n">
-        <v>-0.6805</v>
+        <v>-0.6829</v>
       </c>
       <c r="Q24" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R24" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.5344</v>
+        <v>0.0384</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.3478</v>
+        <v>0.0068</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.1866</v>
+        <v>0.0316</v>
       </c>
       <c r="V24" t="n">
-        <v>-2.8924</v>
+        <v>-2.8814</v>
       </c>
       <c r="W24" t="n">
         <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>-2.8924</v>
+        <v>-2.8814</v>
       </c>
     </row>
     <row r="25">
@@ -2359,67 +2359,67 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>6.595599999999999</v>
+        <v>7.378299999999999</v>
       </c>
       <c r="E25" t="n">
-        <v>0.8639999999999992</v>
+        <v>0.5762999999999998</v>
       </c>
       <c r="F25" t="n">
-        <v>5.7314</v>
+        <v>6.8021</v>
       </c>
       <c r="G25" t="n">
-        <v>4.170199999999999</v>
+        <v>4.1648</v>
       </c>
       <c r="H25" t="n">
-        <v>4.1701</v>
+        <v>4.164899999999999</v>
       </c>
       <c r="I25" t="n">
-        <v>0</v>
+        <v>-0.0001000000000000445</v>
       </c>
       <c r="J25" t="n">
-        <v>7.1594</v>
+        <v>6.935200000000001</v>
       </c>
       <c r="K25" t="n">
-        <v>6.387200000000001</v>
+        <v>6.254100000000001</v>
       </c>
       <c r="L25" t="n">
-        <v>0.7721999999999998</v>
+        <v>0.6811000000000001</v>
       </c>
       <c r="M25" t="n">
-        <v>-2.989200000000001</v>
+        <v>-2.7703</v>
       </c>
       <c r="N25" t="n">
-        <v>-2.217</v>
+        <v>-2.0892</v>
       </c>
       <c r="O25" t="n">
-        <v>-0.7721999999999998</v>
+        <v>-0.6811</v>
       </c>
       <c r="P25" t="n">
-        <v>-3.4024</v>
+        <v>-3.414400000000001</v>
       </c>
       <c r="Q25" t="n">
-        <v>-14.7443</v>
+        <v>-14.7963</v>
       </c>
       <c r="R25" t="n">
-        <v>11.3417</v>
+        <v>11.3817</v>
       </c>
       <c r="S25" t="n">
-        <v>4.1887</v>
+        <v>4.9937</v>
       </c>
       <c r="T25" t="n">
-        <v>1.0889</v>
+        <v>1.1113</v>
       </c>
       <c r="U25" t="n">
-        <v>3.099900000000001</v>
+        <v>3.8825</v>
       </c>
       <c r="V25" t="n">
-        <v>1.6389</v>
+        <v>1.6342</v>
       </c>
       <c r="W25" t="n">
-        <v>7.359599999999999</v>
+        <v>7.3256</v>
       </c>
       <c r="X25" t="n">
-        <v>-5.720599999999999</v>
+        <v>-5.6914</v>
       </c>
     </row>
   </sheetData>

--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104526_W8.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104526_W8.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X25"/>
+  <dimension ref="A1:Y25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -627,6 +632,11 @@
       <c r="X2" t="n">
         <v>0</v>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_104526_W8.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -705,6 +715,11 @@
       <c r="X3" t="n">
         <v>0</v>
       </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_104526_W8.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -783,6 +798,11 @@
       <c r="X4" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_104526_W8.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -861,6 +881,11 @@
       <c r="X5" t="n">
         <v>0</v>
       </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_104526_W8.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -939,6 +964,11 @@
       <c r="X6" t="n">
         <v>0</v>
       </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_104526_W8.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1017,6 +1047,11 @@
       <c r="X7" t="n">
         <v>0</v>
       </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_104526_W8.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1095,6 +1130,11 @@
       <c r="X8" t="n">
         <v>0</v>
       </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_104526_W8.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1173,6 +1213,11 @@
       <c r="X9" t="n">
         <v>-1.2472</v>
       </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_104526_W8.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1251,6 +1296,11 @@
       <c r="X10" t="n">
         <v>-2.1789</v>
       </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_104526_W8.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1329,6 +1379,11 @@
       <c r="X11" t="n">
         <v>-4.5157</v>
       </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_104526_W8.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1407,6 +1462,11 @@
       <c r="X12" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>play_by_play_104526_W8.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1485,6 +1545,11 @@
       <c r="X13" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>play_by_play_104526_W8.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1563,6 +1628,7 @@
       <c r="X14" t="n">
         <v>-8.415199999999999</v>
       </c>
+      <c r="Y14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1641,6 +1707,11 @@
       <c r="X15" t="n">
         <v>0</v>
       </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_104526_W8.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1719,6 +1790,11 @@
       <c r="X16" t="n">
         <v>-0.3155</v>
       </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_104526_W8.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1797,6 +1873,11 @@
       <c r="X17" t="n">
         <v>0</v>
       </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_104526_W8.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1875,6 +1956,11 @@
       <c r="X18" t="n">
         <v>0</v>
       </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_104526_W8.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1953,6 +2039,11 @@
       <c r="X19" t="n">
         <v>0</v>
       </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_104526_W8.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2031,6 +2122,11 @@
       <c r="X20" t="n">
         <v>0.2292</v>
       </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_104526_W8.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2109,6 +2205,11 @@
       <c r="X21" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_104526_W8.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2187,6 +2288,11 @@
       <c r="X22" t="n">
         <v>-1.6342</v>
       </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_104526_W8.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2265,6 +2371,11 @@
       <c r="X23" t="n">
         <v>0</v>
       </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_104526_W8.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2343,6 +2454,11 @@
       <c r="X24" t="n">
         <v>-2.8814</v>
       </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>play_by_play_104526_W8.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2421,6 +2537,7 @@
       <c r="X25" t="n">
         <v>-5.6914</v>
       </c>
+      <c r="Y25" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
